--- a/周维度经营看板上传模板.xlsx
+++ b/周维度经营看板上传模板.xlsx
@@ -1,19 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JunJun\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23340" windowHeight="6154"/>
+    <workbookView windowWidth="21000" windowHeight="14005" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="填写说明" sheetId="8" r:id="rId1"/>
+    <sheet name="订单数据" sheetId="1" r:id="rId1"/>
     <sheet name="采购数据统计" sheetId="2" r:id="rId2"/>
     <sheet name="Key-SKU断货统计" sheetId="3" r:id="rId3"/>
     <sheet name="议价数据统计" sheetId="4" r:id="rId4"/>
     <sheet name="仓储单位产出" sheetId="5" r:id="rId5"/>
     <sheet name="效率提升" sheetId="6" r:id="rId6"/>
     <sheet name="库存周转分析" sheetId="7" r:id="rId7"/>
+    <sheet name="总结" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,51 +38,88 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown User</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+上周备货较多，本周趋于稳定，上周涨幅主要以常规为主</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+  - 蔡伟凤</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
-  <si>
-    <t>周维度经营看板上传模板</t>
-  </si>
-  <si>
-    <t>说明项</t>
-  </si>
-  <si>
-    <t>填写要求</t>
-  </si>
-  <si>
-    <t>周次格式</t>
-  </si>
-  <si>
-    <t>建议填写 07-30、2026-W31 或 本周日期</t>
-  </si>
-  <si>
-    <t>首行</t>
-  </si>
-  <si>
-    <t>每张表第一行写表头，不要留空</t>
-  </si>
-  <si>
-    <t>金额字段</t>
-  </si>
-  <si>
-    <t>填写纯数字，不要手动加逗号</t>
-  </si>
-  <si>
-    <t>比例字段</t>
-  </si>
-  <si>
-    <t>填写 0.453 或 45.3% 都可以</t>
-  </si>
-  <si>
-    <t>备注字段</t>
-  </si>
-  <si>
-    <t>可为空，用于展示运营说明</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>周次</t>
   </si>
   <si>
+    <t>新下单订单条数</t>
+  </si>
+  <si>
+    <t>新下单订单金额</t>
+  </si>
+  <si>
+    <t>待审核总订单条数</t>
+  </si>
+  <si>
+    <t>待审核总订单金额</t>
+  </si>
+  <si>
+    <t>25年及以前待审核订单条数</t>
+  </si>
+  <si>
+    <t>25年及以前待审核订单金额</t>
+  </si>
+  <si>
+    <t>26年1-6月待审核订单条数</t>
+  </si>
+  <si>
+    <t>26年1-6月待审核订单金额</t>
+  </si>
+  <si>
+    <t>环比</t>
+  </si>
+  <si>
+    <t>07-30</t>
+  </si>
+  <si>
+    <t>08-06</t>
+  </si>
+  <si>
     <t>采购合同个数</t>
   </si>
   <si>
@@ -110,7 +153,7 @@
     <t>07-23</t>
   </si>
   <si>
-    <t>07-30</t>
+    <t>08-07</t>
   </si>
   <si>
     <t>货号个数</t>
@@ -143,33 +186,60 @@
     <t>月份</t>
   </si>
   <si>
-    <t>主仓单位面积销售额</t>
-  </si>
-  <si>
-    <t>廊坊仓单位面积销售额</t>
-  </si>
-  <si>
-    <t>广州仓单位面积销售额</t>
-  </si>
-  <si>
-    <t>成都仓单位面积销售额</t>
-  </si>
-  <si>
-    <t>主仓单位面积毛利</t>
-  </si>
-  <si>
-    <t>廊坊仓单位面积毛利</t>
-  </si>
-  <si>
-    <t>广州仓单位面积毛利</t>
-  </si>
-  <si>
-    <t>成都仓单位面积毛利</t>
+    <t>主仓面积</t>
+  </si>
+  <si>
+    <t>廊坊仓面积</t>
+  </si>
+  <si>
+    <t>成都仓面积</t>
+  </si>
+  <si>
+    <t>广州仓面积</t>
+  </si>
+  <si>
+    <t>主仓每平米销售额</t>
+  </si>
+  <si>
+    <t>廊坊每平米销售额</t>
+  </si>
+  <si>
+    <t>成都每平米销售额</t>
+  </si>
+  <si>
+    <t>广州仓每平米销售额</t>
+  </si>
+  <si>
+    <t>主仓每平米毛利</t>
+  </si>
+  <si>
+    <t>廊坊每平米毛利</t>
+  </si>
+  <si>
+    <t>成都每平米毛利</t>
+  </si>
+  <si>
+    <t>广州仓每平米毛利</t>
+  </si>
+  <si>
+    <t>主仓租金</t>
+  </si>
+  <si>
+    <t>廊坊仓租金</t>
+  </si>
+  <si>
+    <t>成都仓租金</t>
+  </si>
+  <si>
+    <t>广州仓租金</t>
   </si>
   <si>
     <t>2026-06</t>
   </si>
   <si>
+    <t>2026-07</t>
+  </si>
+  <si>
     <t>模块</t>
   </si>
   <si>
@@ -188,7 +258,16 @@
     <t>年度协议管理打通；标签自动流转模块沟通</t>
   </si>
   <si>
-    <t>08-06</t>
+    <t>知识库:
+①文件 URL 规范化,修复中文文件名和空格导致链接打不开的问题口径。
+②知识库龙虾待IT开通商品详情页端口后再开放给销售。
+报价:
+①耗材搜索排序 V1回归中：框架集成完成，12 个基础自动化测试通过，进入真实业务 Case 回归. 
+②AI任务分流内测试运行：子代理分流可执行，日报改为人工触发验证口径
+端口进展
+自动关联：采购单中心、销售成品采购任务两个8月底完成
+9月开展：自动生产转换——联动库存+占用+阈值+大小包装：
+时间待定：自动收票——待收票（成品）</t>
   </si>
   <si>
     <t>仓库/品类</t>
@@ -239,7 +318,16 @@
     <t>广州所有商品</t>
   </si>
   <si>
+    <t>宜昌所有商品</t>
+  </si>
+  <si>
     <t>全部在售库库存合计</t>
+  </si>
+  <si>
+    <t>本周小结</t>
+  </si>
+  <si>
+    <t>KEY-SKY断货率进一步降低到2%，新下单金额上涨81%，7月廊坊仓面积从1300平降低到1100平</t>
   </si>
 </sst>
 </file>
@@ -254,13 +342,19 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="27">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -268,36 +362,41 @@
       <color rgb="FF284D79"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -305,7 +404,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -313,7 +412,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -321,7 +420,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -329,7 +428,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -337,14 +436,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -352,7 +451,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -360,7 +459,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -368,14 +467,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -383,47 +482,65 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,13 +549,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE5B9B7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEAF3FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2D6FB8"/>
+        <fgColor rgb="FFB2A2C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCC1D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3D69B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,29 +887,22 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -783,156 +911,221 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="37">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -985,7 +1178,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1037,12 +1230,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1069,14 +1262,15 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1103,6 +1297,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1114,160 +1309,131 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1278,718 +1444,1034 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelRow="7" outlineLevelCol="1"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="19.6936936936937" customWidth="1"/>
-    <col min="2" max="2" width="43.1621621621622" customWidth="1"/>
+    <col min="6" max="6" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1627906976744" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.8294573643411" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" spans="1:2">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="40.5" customHeight="1" spans="1:10">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="16" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="C1" s="34" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="17" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="E1" s="34" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="17" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="17" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="17" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="17" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:10">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="17" t="s">
+      <c r="B2" s="14">
+        <v>5191</v>
+      </c>
+      <c r="C2" s="35">
+        <v>6571276.82</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1946</v>
+      </c>
+      <c r="E2" s="23">
+        <v>10539098.29</v>
+      </c>
+      <c r="F2" s="1">
+        <v>102</v>
+      </c>
+      <c r="G2" s="1">
+        <v>459589.47</v>
+      </c>
+      <c r="H2" s="1">
+        <v>431</v>
+      </c>
+      <c r="I2" s="1">
+        <v>4389773.64</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:10">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>12</v>
+      <c r="B3" s="1">
+        <v>4684</v>
+      </c>
+      <c r="C3" s="23">
+        <v>11875244.04</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1981</v>
+      </c>
+      <c r="E3" s="23">
+        <v>15540809.43</v>
+      </c>
+      <c r="F3" s="1">
+        <v>98</v>
+      </c>
+      <c r="G3" s="1">
+        <v>455024.27</v>
+      </c>
+      <c r="H3" s="1">
+        <v>356</v>
+      </c>
+      <c r="I3" s="1">
+        <v>3925227.65</v>
+      </c>
+      <c r="J3" s="36">
+        <f>(C3-C2)/C2</f>
+        <v>0.807144085584268</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="2"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="11" width="18" customWidth="1"/>
+    <col min="1" max="1" width="6.82945736434108" style="1" customWidth="1"/>
+    <col min="2" max="6" width="18" style="25" customWidth="1"/>
+    <col min="7" max="7" width="18" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.16279069767442" style="25" customWidth="1"/>
+    <col min="9" max="9" width="19" style="1" customWidth="1"/>
+    <col min="10" max="11" width="18" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="10" t="s">
+    <row r="1" customHeight="1" spans="1:11">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="D1" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="H1" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="J1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="K1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="10" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:11">
+      <c r="A2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="B2" s="29">
+        <v>1039</v>
+      </c>
+      <c r="C2" s="29">
+        <v>2486</v>
+      </c>
+      <c r="D2" s="30">
+        <v>1169</v>
+      </c>
+      <c r="E2" s="30">
+        <v>521</v>
+      </c>
+      <c r="F2" s="31">
+        <v>0.446</v>
+      </c>
+      <c r="G2" s="7">
+        <v>4141198.82</v>
+      </c>
+      <c r="H2" s="32">
+        <v>15</v>
+      </c>
+      <c r="I2" s="7">
+        <v>276079.92</v>
+      </c>
+      <c r="J2" s="7">
+        <v>165.7</v>
+      </c>
+      <c r="K2" s="24"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:11">
+      <c r="A3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="29">
+        <v>1169</v>
+      </c>
+      <c r="C3" s="29">
+        <v>3698</v>
+      </c>
+      <c r="D3" s="30">
+        <v>1138</v>
+      </c>
+      <c r="E3" s="30">
+        <v>515</v>
+      </c>
+      <c r="F3" s="31">
+        <v>0.453</v>
+      </c>
+      <c r="G3" s="7">
+        <v>5760008.07</v>
+      </c>
+      <c r="H3" s="32">
+        <v>15</v>
+      </c>
+      <c r="I3" s="7">
+        <v>384000.54</v>
+      </c>
+      <c r="J3" s="7">
+        <v>246.5</v>
+      </c>
+      <c r="K3" s="24">
+        <v>0.391</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:11">
+      <c r="A4" s="37" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1039</v>
-      </c>
-      <c r="C2" s="3">
-        <v>2486</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1169</v>
-      </c>
-      <c r="E2" s="3">
-        <v>521</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.446</v>
-      </c>
-      <c r="G2" s="5">
-        <v>4141198.82</v>
-      </c>
-      <c r="H2" s="3">
+      <c r="B4" s="29">
+        <v>845</v>
+      </c>
+      <c r="C4" s="29">
+        <v>2042</v>
+      </c>
+      <c r="D4" s="30">
+        <v>893</v>
+      </c>
+      <c r="E4" s="30">
+        <v>448</v>
+      </c>
+      <c r="F4" s="31">
+        <f>E4/D4</f>
+        <v>0.501679731243001</v>
+      </c>
+      <c r="G4" s="7">
+        <v>4556368.56</v>
+      </c>
+      <c r="H4" s="32">
         <v>15</v>
       </c>
-      <c r="I2" s="5">
-        <v>276079.92</v>
-      </c>
-      <c r="J2" s="5">
-        <v>165.7</v>
-      </c>
-      <c r="K2" s="13"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1169</v>
-      </c>
-      <c r="C3" s="3">
-        <v>3698</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1138</v>
-      </c>
-      <c r="E3" s="3">
-        <v>515</v>
-      </c>
-      <c r="F3" s="13">
-        <v>0.453</v>
-      </c>
-      <c r="G3" s="5">
-        <v>5760008.07</v>
-      </c>
-      <c r="H3" s="3">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5">
-        <v>384000.54</v>
-      </c>
-      <c r="J3" s="5">
-        <v>246.5</v>
-      </c>
-      <c r="K3" s="13">
-        <v>0.391</v>
+      <c r="I4" s="7">
+        <f>G4/H4</f>
+        <v>303757.904</v>
+      </c>
+      <c r="J4" s="7">
+        <f>C4/H4</f>
+        <v>136.133333333333</v>
+      </c>
+      <c r="K4" s="24">
+        <f>(G4-G3)/G3</f>
+        <v>-0.208964899939802</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="2" outlineLevelCol="4"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="5" width="18" customWidth="1"/>
+    <col min="1" max="5" width="18" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" customHeight="1" spans="1:5">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="10" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:5">
+      <c r="A2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="5">
+        <v>2264</v>
+      </c>
+      <c r="C2" s="5">
+        <v>48</v>
+      </c>
+      <c r="D2" s="24">
+        <v>0.0212</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="10" t="s">
+    </row>
+    <row r="3" customHeight="1" spans="1:5">
+      <c r="A3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2248</v>
+      </c>
+      <c r="C3" s="5">
+        <v>69</v>
+      </c>
+      <c r="D3" s="24">
+        <v>0.0307</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="3">
-        <v>2264</v>
-      </c>
-      <c r="C2" s="3">
-        <v>48</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0212</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="3">
+    <row r="4" customHeight="1" spans="1:5">
+      <c r="A4" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5">
         <v>2248</v>
       </c>
-      <c r="C3" s="3">
-        <v>69</v>
-      </c>
-      <c r="D3" s="13">
-        <v>0.0307</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>31</v>
+      <c r="C4" s="1">
+        <v>46</v>
+      </c>
+      <c r="D4" s="24">
+        <f>C4/B4</f>
+        <v>0.0204626334519573</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="4" width="18" customWidth="1"/>
+    <col min="1" max="4" width="18" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" customHeight="1" spans="1:4">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="5">
+    </row>
+    <row r="2" customHeight="1" spans="1:4">
+      <c r="A2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="7">
         <v>4971.97</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="7">
         <v>56502.88</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="7">
         <v>61474.85</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="5">
+    <row r="3" customHeight="1" spans="1:4">
+      <c r="A3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="7">
         <v>5210.54</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="7">
         <v>25998.03</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="7">
         <v>31208.57</v>
       </c>
     </row>
+    <row r="4" customHeight="1" spans="1:4">
+      <c r="A4" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="7">
+        <v>17901.513</v>
+      </c>
+      <c r="C4" s="7">
+        <v>5144.33</v>
+      </c>
+      <c r="D4" s="7">
+        <f>B4+C4</f>
+        <v>23045.843</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="1"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="9" width="14.1261261261261" customWidth="1"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="5" width="14.1627906976744" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="7" max="9" width="14.1627906976744" style="1" customWidth="1"/>
+    <col min="10" max="13" width="12.8294573643411" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.3" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="3" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="17" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="s">
+      <c r="L1" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="5">
-        <v>1814</v>
-      </c>
-      <c r="C2" s="5">
-        <v>1092</v>
-      </c>
-      <c r="D2" s="5">
-        <v>519</v>
-      </c>
-      <c r="E2" s="5">
-        <v>558</v>
-      </c>
-      <c r="F2" s="5">
-        <v>544</v>
-      </c>
-      <c r="G2" s="5">
-        <v>290</v>
-      </c>
-      <c r="H2" s="5">
-        <v>184</v>
-      </c>
-      <c r="I2" s="5">
-        <v>198</v>
+      <c r="M1" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:17">
+      <c r="A2" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="19">
+        <v>8446</v>
+      </c>
+      <c r="C2" s="19">
+        <v>1301</v>
+      </c>
+      <c r="D2" s="19">
+        <v>1040</v>
+      </c>
+      <c r="E2" s="19">
+        <v>1202</v>
+      </c>
+      <c r="F2" s="20">
+        <v>1814.43594600995</v>
+      </c>
+      <c r="G2" s="20">
+        <v>1091.67947732513</v>
+      </c>
+      <c r="H2" s="20">
+        <v>558.466346153846</v>
+      </c>
+      <c r="I2" s="20">
+        <v>519.371048252912</v>
+      </c>
+      <c r="J2" s="21">
+        <v>543.79694529955</v>
+      </c>
+      <c r="K2" s="21">
+        <v>289.948501152959</v>
+      </c>
+      <c r="L2" s="21">
+        <v>197.801923076923</v>
+      </c>
+      <c r="M2" s="21">
+        <v>184.280366056572</v>
+      </c>
+      <c r="N2" s="19">
+        <v>225323</v>
+      </c>
+      <c r="O2" s="19">
+        <v>33193</v>
+      </c>
+      <c r="P2" s="19">
+        <v>24736</v>
+      </c>
+      <c r="Q2" s="19">
+        <v>22844</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:17">
+      <c r="A3" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="19">
+        <v>8446</v>
+      </c>
+      <c r="C3" s="19">
+        <v>1100</v>
+      </c>
+      <c r="D3" s="19">
+        <v>1040</v>
+      </c>
+      <c r="E3" s="19">
+        <v>1202</v>
+      </c>
+      <c r="F3" s="22">
+        <f>18279769/B3</f>
+        <v>2164.31079801089</v>
+      </c>
+      <c r="G3" s="22">
+        <f>2542454/C3</f>
+        <v>2311.32181818182</v>
+      </c>
+      <c r="H3" s="22">
+        <f>727465/D3</f>
+        <v>699.485576923077</v>
+      </c>
+      <c r="I3" s="22">
+        <f>955153/E3</f>
+        <v>794.636439267887</v>
+      </c>
+      <c r="J3" s="23">
+        <f>5257975/B3</f>
+        <v>622.540255742363</v>
+      </c>
+      <c r="K3" s="23">
+        <f>629021/C3</f>
+        <v>571.837272727273</v>
+      </c>
+      <c r="L3" s="23">
+        <f>251054/D3</f>
+        <v>241.398076923077</v>
+      </c>
+      <c r="M3" s="23">
+        <f>275215/E3</f>
+        <v>228.964226289517</v>
+      </c>
+      <c r="N3" s="19">
+        <v>225323</v>
+      </c>
+      <c r="O3" s="19">
+        <v>33193</v>
+      </c>
+      <c r="P3" s="19">
+        <v>24736</v>
+      </c>
+      <c r="Q3" s="19">
+        <v>22844</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="3" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="11.963963963964" customWidth="1"/>
-    <col min="2" max="2" width="12.9009009009009" customWidth="1"/>
-    <col min="3" max="3" width="39.6936936936937" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.8294573643411" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.6666666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" ht="14.15" spans="1:3">
-      <c r="A2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" ht="14.15" spans="1:3">
-      <c r="A3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>47</v>
+    <row r="1" customHeight="1" spans="1:3">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:3">
+      <c r="A3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" ht="229.5" customHeight="1" spans="1:3">
+      <c r="A4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="7"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="21.3873873873874" customWidth="1"/>
-    <col min="2" max="2" width="13.8918918918919" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="6" width="13.8918918918919" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1441441441441" customWidth="1"/>
-    <col min="8" max="11" width="12.5045045045045" customWidth="1"/>
+    <col min="1" max="1" width="21.3333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.8294573643411" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.6666666666667" style="3" customWidth="1"/>
+    <col min="4" max="6" width="13.8294573643411" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.1627906976744" style="1" customWidth="1"/>
+    <col min="8" max="11" width="12.4961240310078" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.3" spans="1:11">
-      <c r="A1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="2" t="s">
+    <row r="1" s="3" customFormat="1" ht="27" customHeight="1" spans="1:11">
+      <c r="A1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4">
+      <c r="F1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:11">
+      <c r="A2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="6">
         <v>12960913.76</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="6">
         <v>59780928.78</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="6">
         <v>4.61</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="6">
         <v>79.1</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="6">
         <v>14129745.66</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="7">
         <v>57251892.44</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="7">
         <v>4.05</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="7">
         <v>90.1</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="8">
         <v>0.09</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="4">
+    <row r="3" customHeight="1" spans="1:11">
+      <c r="A3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="6">
         <v>32900585.42</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="6">
         <v>134744245.49</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="6">
         <v>4.1</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="6">
         <v>89.1</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="6">
         <v>34198877.49</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="7">
         <v>131835427.48</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="7">
         <v>3.85</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="7">
         <v>94.7</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="8">
         <v>0.039</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="7">
         <v>5.6</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="4">
+    <row r="4" customHeight="1" spans="1:11">
+      <c r="A4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="6">
         <v>1979750.45</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>14321547.68</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="6">
         <v>7.23</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="6">
         <v>50.5</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="6">
         <v>1851979.97</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="7">
         <v>13356804.36</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="7">
         <v>7.21</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="7">
         <v>50.6</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="8">
         <v>-0.065</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="7">
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="4">
+    <row r="5" customHeight="1" spans="1:11">
+      <c r="A5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="6">
         <v>3506939.44</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>31251759.68</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="3">
         <v>8.91</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="6">
         <v>41</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>3502534.97</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="10">
         <v>32057459.56</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="7">
         <v>9.15</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="7">
         <v>39.9</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="8">
         <v>-0.001</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="7">
         <v>-1.1</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="4">
+    <row r="6" customHeight="1" spans="1:11">
+      <c r="A6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="6">
         <v>1367089.88</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="9">
         <v>14437535.33</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="3">
         <v>10.56</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="6">
         <v>34.6</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <v>1345513.08</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="10">
         <v>12785473.64</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="7">
         <v>9.5</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="7">
         <v>38.4</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="8">
         <v>-0.016</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="7">
         <v>3.8</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="4">
-        <v>52607947.16</v>
-      </c>
-      <c r="C7" s="7">
+    <row r="7" ht="14.25" customHeight="1" spans="1:11">
+      <c r="A7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="6">
+        <v>11818000</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>11747000</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1" spans="1:11">
+      <c r="A8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="6">
+        <f>SUM(B3:B7)</f>
+        <v>51572365.19</v>
+      </c>
+      <c r="C8" s="6">
+        <f>SUM(C3:C7)</f>
         <v>194755088.18</v>
       </c>
-      <c r="D7" s="9">
-        <v>3.7</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D8" s="11">
+        <f>C8/B8</f>
+        <v>3.77634586784016</v>
+      </c>
+      <c r="E8" s="6">
         <v>98.6</v>
       </c>
-      <c r="F7" s="7">
-        <v>53624769.53</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="F8" s="6">
+        <f>SUM(F3:F7)</f>
+        <v>52645905.51</v>
+      </c>
+      <c r="G8" s="6">
+        <f>SUM(G3:G7)</f>
         <v>190035165.04</v>
       </c>
-      <c r="H7" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="I7" s="5">
+      <c r="H8" s="7">
+        <f>G8/F8</f>
+        <v>3.60968556242048</v>
+      </c>
+      <c r="I8" s="7">
         <v>103</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J8" s="8">
         <v>0.019</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K8" s="7">
         <v>4.4</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="F8" s="7"/>
+    <row r="9" customHeight="1" spans="1:11">
+      <c r="F9" s="9"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="1" outlineLevelCol="1"/>
+  <cols>
+    <col min="2" max="2" width="28.5038759689922" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1627906976744" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.6666666666667" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/周维度经营看板上传模板.xlsx
+++ b/周维度经营看板上传模板.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="14005" firstSheet="1" activeTab="7"/>
+    <workbookView windowWidth="21000" windowHeight="11074"/>
   </bookViews>
   <sheets>
     <sheet name="订单数据" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="81">
   <si>
     <t>周次</t>
   </si>
@@ -328,6 +328,12 @@
   </si>
   <si>
     <t>KEY-SKY断货率进一步降低到2%，新下单金额上涨81%，7月廊坊仓面积从1300平降低到1100平</t>
+  </si>
+  <si>
+    <t>08-01</t>
+  </si>
+  <si>
+    <t>08-10</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1041,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1121,6 +1127,22 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment/>
+      <extLst>
+        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
+          <etc:displayText val="2"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment/>
+      <extLst>
+        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
+          <etc:displayText val="2"/>
+        </ext>
+      </extLst>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1"/>
@@ -1522,17 +1544,17 @@
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="36">
         <v>4684</v>
       </c>
-      <c r="C3" s="23">
-        <v>11875244.04</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1981</v>
-      </c>
-      <c r="E3" s="23">
-        <v>15540809.43</v>
+      <c r="C3" s="37">
+        <v>8243621.3</v>
+      </c>
+      <c r="D3" s="36">
+        <v>1917</v>
+      </c>
+      <c r="E3" s="37">
+        <v>11528192.33</v>
       </c>
       <c r="F3" s="1">
         <v>98</v>
@@ -1546,9 +1568,9 @@
       <c r="I3" s="1">
         <v>3925227.65</v>
       </c>
-      <c r="J3" s="36">
+      <c r="J3" s="38">
         <f>(C3-C2)/C2</f>
-        <v>0.807144085584268</v>
+        <v>0.254493080387382</v>
       </c>
     </row>
   </sheetData>
@@ -1677,7 +1699,7 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="39" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="29">
@@ -1785,7 +1807,7 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="40" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="5">
@@ -1859,7 +1881,7 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:4">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="40" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="7">
@@ -2001,7 +2023,7 @@
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:17">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="41" t="s">
         <v>51</v>
       </c>
       <c r="B3" s="19">
@@ -2446,8 +2468,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="28.5038759689922" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.1627906976744" style="1" customWidth="1"/>
@@ -2470,6 +2492,22 @@
         <v>78</v>
       </c>
     </row>
+    <row r="3" customHeight="1" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="1">
+        <v>666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
